--- a/results/Int Task Remove ACC 0.4/Rando_8_permute.xlsx
+++ b/results/Int Task Remove ACC 0.4/Rando_8_permute.xlsx
@@ -440,277 +440,277 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5466117417149843</v>
+        <v>0.520907639131015</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.545968654898264</v>
+        <v>0.5192999220892144</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.545968654898264</v>
+        <v>0.5239590731629626</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5436390793613899</v>
+        <v>0.5266101921081969</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.53791026915809</v>
+        <v>0.5266364493343147</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5273385072982175</v>
+        <v>0.5186305780463764</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5233487002673072</v>
+        <v>0.52023183839323</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5183680057851987</v>
+        <v>0.5147393432249899</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5197066938708748</v>
+        <v>0.5137747129999096</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.514187941476517</v>
+        <v>0.5049290409225325</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.4831618004709083</v>
+        <v>0.5002109187016017</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4820133696630036</v>
+        <v>0.469873491823672</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.4850385464688335</v>
+        <v>0.469873491823672</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4756677298691013</v>
+        <v>0.4758450737569787</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.4763370739119393</v>
+        <v>0.4758450737569787</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.4773017041370197</v>
+        <v>0.4758450737569787</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4766586173202994</v>
+        <v>0.4697357489981362</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4809174533073344</v>
+        <v>0.4717239805954794</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.4809174533073344</v>
+        <v>0.4829190287409015</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4803531381689674</v>
+        <v>0.4805106815256739</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4647025400637921</v>
+        <v>0.4702738069103854</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4611720192667778</v>
+        <v>0.4816526556386317</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4611982764928955</v>
+        <v>0.4945737935665492</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.467976945294576</v>
+        <v>0.4871649513380424</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.461920134987969</v>
+        <v>0.4878080381547627</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.4622416783963292</v>
+        <v>0.4871386941119247</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.4602599034939329</v>
+        <v>0.4738960127756471</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.4599383600855727</v>
+        <v>0.4680032025206937</v>
       </c>
     </row>
     <row r="30">
@@ -720,137 +720,137 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.4576875562270518</v>
+        <v>0.467412630156209</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4564013825936113</v>
+        <v>0.4890942117882032</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.4576875562270518</v>
+        <v>0.4994757163703044</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.4751296719568521</v>
+        <v>0.4991541729619442</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4757465015474546</v>
+        <v>0.4977039992768502</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4780760770843288</v>
+        <v>0.4928545909253305</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4776757619976154</v>
+        <v>0.4918439029429616</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4836012861736335</v>
+        <v>0.5069108158249289</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.4839490868081113</v>
+        <v>0.5099622498568765</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4836012861736335</v>
+        <v>0.51036256494359</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4845659163987138</v>
+        <v>0.4904328998738792</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4819935691318328</v>
+        <v>0.4913841862627358</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4819935691318328</v>
+        <v>0.479723395188471</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4823151125401929</v>
+        <v>0.4790803083717507</v>
       </c>
     </row>
     <row r="44">
@@ -860,233 +860,233 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4845659163987138</v>
+        <v>0.4776628486077213</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4848874598070739</v>
+        <v>0.48742752359922</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4865214340749924</v>
+        <v>0.498051799911328</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4792047073610627</v>
+        <v>0.4771252211418019</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4918761864176965</v>
+        <v>0.4771252211418019</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4912330996009763</v>
+        <v>0.4978085977349914</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4830107138091487</v>
+        <v>0.4947963343190555</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4878076077084329</v>
+        <v>0.4987271702027832</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4878076077084329</v>
+        <v>0.5032287779198251</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4961677363257962</v>
+        <v>0.5032287779198251</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4961677363257962</v>
+        <v>0.5032287779198251</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5134398257553257</v>
+        <v>0.5006172600369323</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5060443273630427</v>
+        <v>0.5035438646332382</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5321750022598433</v>
+        <v>0.5142271120925288</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5422216195973605</v>
+        <v>0.5146140833430184</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5121532216755553</v>
+        <v>0.521924353362001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5141875110301872</v>
+        <v>0.5189254337822888</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5084324436007697</v>
+        <v>0.5067984693328512</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5020080321285141</v>
+        <v>0.5067984693328512</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5</v>
+        <v>0.5067984693328512</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5</v>
+        <v>0.5003478006344779</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5</v>
+        <v>0.5003478006344779</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5</v>
+        <v>0.5003478006344779</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1096,7 +1096,7 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1106,7 +1106,7 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1116,7 +1116,7 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1126,7 +1126,7 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1136,7 +1136,7 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1146,7 +1146,7 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1156,7 +1156,7 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1166,7 +1166,7 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1176,7 +1176,7 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -1186,7 +1186,7 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -1196,77 +1196,77 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5</v>
+        <v>0.500669344042838</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5</v>
+        <v>0.500669344042838</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5</v>
+        <v>0.500669344042838</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5</v>
+        <v>0.500669344042838</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5</v>
+        <v>0.500669344042838</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5</v>
+        <v>0.500669344042838</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5</v>
+        <v>0.500669344042838</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -1276,7 +1276,7 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -1286,7 +1286,7 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -1296,7 +1296,7 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -1306,7 +1306,7 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -1316,7 +1316,7 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B90" t="n">
